--- a/www/terminologies/CodeSystem-tre-r365-etat-objet.xlsx
+++ b/www/terminologies/CodeSystem-tre-r365-etat-objet.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260827120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-08-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,7 +316,7 @@
     <t>018</t>
   </si>
   <si>
-    <t>EGE fermée suite à cession</t>
+    <t>EGE cédée</t>
   </si>
   <si>
     <t>019</t>
